--- a/django application/Saransha/media/all_authors_publications.xlsx
+++ b/django application/Saransha/media/all_authors_publications.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
   <si>
     <t>Main Author</t>
   </si>
@@ -43,118 +43,133 @@
     <t>Last Search Date</t>
   </si>
   <si>
-    <t>Dr. Jagadishwari V</t>
-  </si>
-  <si>
-    <t>Sentiment analysis of social media text-emoticon post with machine learning models contribution title</t>
-  </si>
-  <si>
-    <t>Link prediction using influencer nodes of a social network</t>
-  </si>
-  <si>
-    <t>Empirical analysis of community detection algorithms</t>
-  </si>
-  <si>
-    <t>Empirical analysis of machine learning models for detecting credit card fraud</t>
-  </si>
-  <si>
-    <t>Comparative study of Deep Learning Models for Covid 19 Diagnosis</t>
-  </si>
-  <si>
-    <t>Sentiment analysis of COVID 19 vaccines using Twitter data</t>
-  </si>
-  <si>
-    <t>Talkative Friend algorithm for inferring ties in social networks</t>
-  </si>
-  <si>
-    <t>Empirical Analysis of Traditional Link Prediction Methods</t>
-  </si>
-  <si>
-    <t>Time series Covid 19 Predictions with Machine Learning Models</t>
-  </si>
-  <si>
-    <t>NBCD: neighborhood based community detection in dynamic social networks</t>
-  </si>
-  <si>
-    <t>Rainfall and outlier rain prediction with ARIMA and ANN models</t>
-  </si>
-  <si>
-    <t>Deep learning models for Covid 19 diagnosis</t>
-  </si>
-  <si>
-    <t>Trace Clustering Techniques for Process Mining</t>
-  </si>
-  <si>
-    <t>CNJC: A cumulative similarity measure for Link Prediction in social networks</t>
+    <t>SUSHEELAMMA K H</t>
+  </si>
+  <si>
+    <t>Student risk identification learning model using machine learning approach</t>
+  </si>
+  <si>
+    <t>A survey on clustering and feature selection algorithm for quickly predicting engineering students’ academic performance</t>
+  </si>
+  <si>
+    <t>Enhancing Academic Performance Prediction: A Novel Approach Using the TabNet Algorithm</t>
+  </si>
+  <si>
+    <t>Deep Learning Algorithms for Recognizing and Digitizing Scanned Kannada Printed and Handwritten Documents</t>
+  </si>
+  <si>
+    <t>AI-ENABLED WATER WELL PREDICTOR</t>
+  </si>
+  <si>
+    <t>AIR AND WATER QUALITY INDEXING AND ENVIRONMENT MONITORING</t>
+  </si>
+  <si>
+    <t>LEARNING BEHAVIOUR ANALYSIS OF MOOC LEARNERS WITH ANN</t>
+  </si>
+  <si>
+    <t>Multiview Clustering with Self Representation and Structural Constraints</t>
+  </si>
+  <si>
+    <t>SUPPLY CHAIN MANAGEMENT USING BLOCK CHAIN</t>
+  </si>
+  <si>
+    <t>ENSEMBLE MACHINE LEARNING MODELS TO PREDICT STUDENTS’ LEARNING BEHAVIOR</t>
+  </si>
+  <si>
+    <t>CRYPTO TRADING BOT USING MOVING AVERAGE, SUPPORT AND RESISTANCE</t>
+  </si>
+  <si>
+    <t>TRAFFIC ACCIDENT EVENT PREDICTION IN TRAFFIC VIDEO USING DEEP LEARNING</t>
+  </si>
+  <si>
+    <t>Student Risk Identification Model Using Random Forest Algorithm</t>
+  </si>
+  <si>
+    <t>DROWSINESS DETECTION OF DRIVERS USING IOT IMAGE PROCESSING AND MACHINE LEARNING TECHNIQUES</t>
+  </si>
+  <si>
+    <t>Int. J. Electr. Comput. Eng 9 (5), 3872-3879, 2019</t>
+  </si>
+  <si>
+    <t>International Journal of Research in Computer Science Engineering and …, 2018</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>International Journal of Computer Applications 121 (2), 2015</t>
-  </si>
-  <si>
-    <t>2021 Emerging Trends in Industry 4.0 (ETI 4.0), 1-4, 2021</t>
-  </si>
-  <si>
-    <t>Journal of Physics: Conference Series 2070 (1), 012079, 2021</t>
-  </si>
-  <si>
-    <t>2020 Second International Conference on Inventive Research in Computing …, 2020</t>
-  </si>
-  <si>
-    <t>2017 Second International Conference on Electrical, Computer and …, 2017</t>
-  </si>
-  <si>
-    <t>AIP Conference Proceedings 2901 (1), 060013, 2023</t>
-  </si>
-  <si>
-    <t>2023 Third International Conference on Advances in Electrical, Computing …, 2023</t>
-  </si>
-  <si>
-    <t>2022 Second International Conference on Artificial Intelligence and Smart …, 2022</t>
-  </si>
-  <si>
-    <t>2021 Third International Conference on Intelligent Communication …, 2021</t>
-  </si>
-  <si>
-    <t>2018 Second International Conference on Intelligent Computing and Control …, 2018</t>
-  </si>
-  <si>
-    <t>AIP Conference Proceedings 2901 (1), 060005, 2023</t>
-  </si>
-  <si>
-    <t>2019 9th International Conference on Advances in Computing and Communication …, 2019</t>
+    <t>International Research Journal of Modernization in Engineering Technology …, 2024</t>
+  </si>
+  <si>
+    <t>International Journal of Advanced Research in Science, Communication and …, 2024</t>
+  </si>
+  <si>
+    <t>International Journal of Advanced Research in Science, Communication and …, 2023</t>
+  </si>
+  <si>
+    <t>International Advanced Research Journal in  Science, Engineering and …, 2022</t>
+  </si>
+  <si>
+    <t>International Journal of Noval Research and Development (IJNRD) 7 (6), 10, 2022</t>
+  </si>
+  <si>
+    <t>International Research Journal of Modernization in Engineering Technology …, 2022</t>
+  </si>
+  <si>
+    <t>European Journal of Molecular &amp; Clinical Medicine (EJMCM) 7 (8), 8, 2020</t>
+  </si>
+  <si>
+    <t>International Conference on Computational Intelligence in Data Science, 3-14, 2025</t>
+  </si>
+  <si>
+    <t>2024 First International Conference on Data, Computation and Communication …, 2024</t>
   </si>
   <si>
     <t>article</t>
   </si>
   <si>
-    <t>V Jagadishwari, A Indulekha, K Raghu, P Harshini</t>
-  </si>
-  <si>
-    <t>V Jagadishwari, S Chakrabarty</t>
-  </si>
-  <si>
-    <t>V Jagadishwari, V Umadevi</t>
-  </si>
-  <si>
-    <t>V Jagadishwari, N Lakshmi Narayan, N Shobha</t>
-  </si>
-  <si>
-    <t>V Jagadishwari, N Shobha</t>
-  </si>
-  <si>
-    <t>V Jagadishwari</t>
-  </si>
-  <si>
-    <t>N Shobha, T Asha, K Seemanthini, V Jagadishwari</t>
-  </si>
-  <si>
-    <t>V Jagadishwari, IV Accamma</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
+    <t>KH Susheelamma, KM Ravikumar</t>
+  </si>
+  <si>
+    <t>KH Susheelamma, SH Brahmananda</t>
+  </si>
+  <si>
+    <t>KH Susheelamma, KM Ravikumar, S Sampath</t>
+  </si>
+  <si>
+    <t>KH Susheelamma, KM Ravikumar, S Sampath, PK HR</t>
+  </si>
+  <si>
+    <t>SS Dr. Susheelamma KH, Annasagaram Lasyapriya</t>
+  </si>
+  <si>
+    <t>DR Dr Susheelamma K H , Basavaraj S Biradar , Bhavana B</t>
+  </si>
+  <si>
+    <t>D Susheelamma KH</t>
+  </si>
+  <si>
+    <t>CGM Susheelamma K H , Balagundla Anvesh , Baligolla Mahidhar , B Manogna Sai</t>
+  </si>
+  <si>
+    <t>SDR Susheelamma K H , Navitha H A , Navya S , Prekshitha D</t>
+  </si>
+  <si>
+    <t>DKMR Susheelamma K H</t>
+  </si>
+  <si>
+    <t>L Susheelamma K H, Harshavardhan , K Lavakishor , K Shashi kumar</t>
+  </si>
+  <si>
+    <t>TSV Mrs. Susheelamma K H, Pavan Kumar N, Shreesha N, Subramanya K</t>
+  </si>
+  <si>
+    <t>KMR Susheelamma K H</t>
+  </si>
+  <si>
+    <t>KH Susheelamma, S Gururaj</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
   </si>
 </sst>
 </file>
@@ -555,22 +570,22 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F2" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -581,25 +596,25 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -610,25 +625,25 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="F4" t="s">
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -639,25 +654,25 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F5" t="s">
         <v>3</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -668,25 +683,25 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F6" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -697,25 +712,25 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -726,25 +741,25 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F8" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="s">
         <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -755,25 +770,25 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -784,25 +799,25 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -813,25 +828,25 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="F11" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -841,20 +856,26 @@
       <c r="B12" t="s">
         <v>20</v>
       </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="E12">
+        <v>2022</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -865,25 +886,25 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F13" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -894,25 +915,25 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="F14" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -922,26 +943,23 @@
       <c r="B15" t="s">
         <v>23</v>
       </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E15">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F15" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
